--- a/Tagihan/2026/September/Ibu Nia.xlsx
+++ b/Tagihan/2026/September/Ibu Nia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\September\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7AF825-4872-4208-B3C8-B86A42C0FBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9507B57-30BE-45E6-B836-55B8EF1C6B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1119,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>17</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G17" s="28">
         <f>D17*F17</f>
-        <v>850000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1230,7 +1230,7 @@
       <c r="F29" s="46"/>
       <c r="G29" s="31">
         <f>SUM(G17:G28)</f>
-        <v>850000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">

--- a/Tagihan/2026/September/Ibu Nia.xlsx
+++ b/Tagihan/2026/September/Ibu Nia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\September\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9507B57-30BE-45E6-B836-55B8EF1C6B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7AF825-4872-4208-B3C8-B86A42C0FBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1119,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>17</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G17" s="28">
         <f>D17*F17</f>
-        <v>1700000</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1230,7 +1230,7 @@
       <c r="F29" s="46"/>
       <c r="G29" s="31">
         <f>SUM(G17:G28)</f>
-        <v>1700000</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
